--- a/tests/fixtures/template_fixture.xlsx
+++ b/tests/fixtures/template_fixture.xlsx
@@ -423,17 +423,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A5:AC7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -1152,10 +1148,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A2:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
@@ -1385,9 +1380,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:H3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
@@ -1421,11 +1417,6 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
           <t>NOTES</t>
         </is>
       </c>
@@ -1462,11 +1453,6 @@
         </is>
       </c>
       <c r="G3" t="inlineStr">
-        <is>
-          <t>desc</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
         <is>
           <t>iface note</t>
         </is>
